--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="175">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -538,6 +538,12 @@
   </si>
   <si>
     <t>جمع کل حساب با احتساب آخرین فاکتور :</t>
+  </si>
+  <si>
+    <t>1405/04/11</t>
+  </si>
+  <si>
+    <t>مغز بادام کیک رانی</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1069,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>1322600</v>
+        <v>1458600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2893,17 +2899,23 @@
     <row r="131" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="8">
         <f t="shared" si="5"/>
-        <v>1322600</v>
-      </c>
-      <c r="B131" s="8"/>
+        <v>1458600</v>
+      </c>
+      <c r="B131" s="8">
+        <v>136000</v>
+      </c>
       <c r="C131" s="8"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
+      <c r="D131" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
         <f t="shared" si="5"/>
-        <v>1322600</v>
+        <v>1458600</v>
       </c>
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
@@ -2913,7 +2925,7 @@
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <f t="shared" si="5"/>
-        <v>1322600</v>
+        <v>1458600</v>
       </c>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
@@ -2923,7 +2935,7 @@
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <f t="shared" si="5"/>
-        <v>1322600</v>
+        <v>1458600</v>
       </c>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
@@ -2933,7 +2945,7 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <f t="shared" si="5"/>
-        <v>1322600</v>
+        <v>1458600</v>
       </c>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -2943,7 +2955,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <f t="shared" si="5"/>
-        <v>1322600</v>
+        <v>1458600</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -2953,7 +2965,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>1322600</v>
+        <v>1458600</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -2963,7 +2975,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>1322600</v>
+        <v>1458600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -2974,7 +2986,7 @@
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>13223600</v>
+        <v>13359600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
@@ -2985,7 +2997,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>1322600</v>
+        <v>1458600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="177">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -544,6 +544,12 @@
   </si>
   <si>
     <t>مغز بادام کیک رانی</t>
+  </si>
+  <si>
+    <t>1405/04/22</t>
+  </si>
+  <si>
+    <t>قهوه پروتئین شیر</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1075,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>1458600</v>
+        <v>1748600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2915,17 +2921,23 @@
     <row r="132" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
         <f t="shared" si="5"/>
-        <v>1458600</v>
-      </c>
-      <c r="B132" s="8"/>
+        <v>1748600</v>
+      </c>
+      <c r="B132" s="8">
+        <v>290000</v>
+      </c>
       <c r="C132" s="8"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="1"/>
+      <c r="D132" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <f t="shared" si="5"/>
-        <v>1458600</v>
+        <v>1748600</v>
       </c>
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
@@ -2935,7 +2947,7 @@
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <f t="shared" si="5"/>
-        <v>1458600</v>
+        <v>1748600</v>
       </c>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
@@ -2945,7 +2957,7 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <f t="shared" si="5"/>
-        <v>1458600</v>
+        <v>1748600</v>
       </c>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -2955,7 +2967,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <f t="shared" si="5"/>
-        <v>1458600</v>
+        <v>1748600</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -2965,7 +2977,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>1458600</v>
+        <v>1748600</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -2975,7 +2987,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>1458600</v>
+        <v>1748600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -2986,7 +2998,7 @@
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>13359600</v>
+        <v>13649600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
@@ -2997,7 +3009,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>1458600</v>
+        <v>1748600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="179">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -550,6 +550,12 @@
   </si>
   <si>
     <t>قهوه پروتئین شیر</t>
+  </si>
+  <si>
+    <t>1405/04/25</t>
+  </si>
+  <si>
+    <t>لیموناد کیک داجستیو</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1081,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>1748600</v>
+        <v>2028600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2937,17 +2943,23 @@
     <row r="133" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <f t="shared" si="5"/>
-        <v>1748600</v>
-      </c>
-      <c r="B133" s="8"/>
+        <v>2028600</v>
+      </c>
+      <c r="B133" s="8">
+        <v>280000</v>
+      </c>
       <c r="C133" s="8"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
+      <c r="D133" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <f t="shared" si="5"/>
-        <v>1748600</v>
+        <v>2028600</v>
       </c>
       <c r="B134" s="8"/>
       <c r="C134" s="8"/>
@@ -2957,7 +2969,7 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <f t="shared" si="5"/>
-        <v>1748600</v>
+        <v>2028600</v>
       </c>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -2967,7 +2979,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <f t="shared" si="5"/>
-        <v>1748600</v>
+        <v>2028600</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -2977,7 +2989,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>1748600</v>
+        <v>2028600</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -2987,7 +2999,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>1748600</v>
+        <v>2028600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -2998,7 +3010,7 @@
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>13649600</v>
+        <v>13929600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
@@ -3009,7 +3021,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>1748600</v>
+        <v>2028600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="180">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -556,6 +556,9 @@
   </si>
   <si>
     <t>لیموناد کیک داجستیو</t>
+  </si>
+  <si>
+    <t>1405/04/27</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1084,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>2028600</v>
+        <v>2064600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2959,17 +2962,23 @@
     <row r="134" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <f t="shared" si="5"/>
-        <v>2028600</v>
-      </c>
-      <c r="B134" s="8"/>
+        <v>2064600</v>
+      </c>
+      <c r="B134" s="8">
+        <v>36000</v>
+      </c>
       <c r="C134" s="8"/>
-      <c r="D134" s="1"/>
-      <c r="E134" s="1"/>
+      <c r="D134" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <f t="shared" si="5"/>
-        <v>2028600</v>
+        <v>2064600</v>
       </c>
       <c r="B135" s="8"/>
       <c r="C135" s="8"/>
@@ -2979,7 +2988,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <f t="shared" si="5"/>
-        <v>2028600</v>
+        <v>2064600</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -2989,7 +2998,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>2028600</v>
+        <v>2064600</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -2999,7 +3008,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>2028600</v>
+        <v>2064600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -3010,7 +3019,7 @@
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>13929600</v>
+        <v>13965600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
@@ -3021,7 +3030,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>2028600</v>
+        <v>2064600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="181">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -559,6 +559,9 @@
   </si>
   <si>
     <t>1405/04/27</t>
+  </si>
+  <si>
+    <t>1405/05/01</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1087,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>2064600</v>
+        <v>1164600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2978,17 +2981,23 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <f t="shared" si="5"/>
-        <v>2064600</v>
+        <v>1164600</v>
       </c>
       <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
-      <c r="D135" s="1"/>
-      <c r="E135" s="1"/>
+      <c r="C135" s="8">
+        <v>900000</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <f t="shared" si="5"/>
-        <v>2064600</v>
+        <v>1164600</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -2998,7 +3007,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>2064600</v>
+        <v>1164600</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -3008,7 +3017,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>2064600</v>
+        <v>1164600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -3023,14 +3032,14 @@
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
-        <v>11901000</v>
+        <v>12801000</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>2064600</v>
+        <v>1164600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="182">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -562,6 +562,9 @@
   </si>
   <si>
     <t>1405/05/01</t>
+  </si>
+  <si>
+    <t>روغنم برنج</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1090,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>1164600</v>
+        <v>3164600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2981,14 +2984,14 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <f t="shared" si="5"/>
-        <v>1164600</v>
-      </c>
-      <c r="B135" s="8"/>
-      <c r="C135" s="8">
-        <v>900000</v>
-      </c>
+        <v>3164600</v>
+      </c>
+      <c r="B135" s="8">
+        <v>1100000</v>
+      </c>
+      <c r="C135" s="8"/>
       <c r="D135" s="1" t="s">
-        <v>26</v>
+        <v>181</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>180</v>
@@ -2997,7 +3000,7 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <f t="shared" si="5"/>
-        <v>1164600</v>
+        <v>3164600</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -3007,7 +3010,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>1164600</v>
+        <v>3164600</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -3017,7 +3020,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>1164600</v>
+        <v>3164600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -3028,18 +3031,18 @@
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>13965600</v>
+        <v>15065600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
-        <v>12801000</v>
+        <v>11901000</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>1164600</v>
+        <v>3164600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="180">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -559,12 +559,6 @@
   </si>
   <si>
     <t>1405/04/27</t>
-  </si>
-  <si>
-    <t>1405/05/01</t>
-  </si>
-  <si>
-    <t>روغنم برنج</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1084,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>3164600</v>
+        <v>2064600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2984,23 +2978,17 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <f t="shared" si="5"/>
-        <v>3164600</v>
-      </c>
-      <c r="B135" s="8">
-        <v>1100000</v>
-      </c>
+        <v>2064600</v>
+      </c>
+      <c r="B135" s="8"/>
       <c r="C135" s="8"/>
-      <c r="D135" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>180</v>
-      </c>
+      <c r="D135" s="1"/>
+      <c r="E135" s="1"/>
     </row>
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <f t="shared" si="5"/>
-        <v>3164600</v>
+        <v>2064600</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -3010,7 +2998,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>3164600</v>
+        <v>2064600</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -3020,7 +3008,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>3164600</v>
+        <v>2064600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -3031,7 +3019,7 @@
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>15065600</v>
+        <v>13965600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
@@ -3042,7 +3030,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>3164600</v>
+        <v>2064600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="181">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -559,6 +559,9 @@
   </si>
   <si>
     <t>1405/04/27</t>
+  </si>
+  <si>
+    <t>1405/05/10</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1087,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>2064600</v>
+        <v>2154600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2978,17 +2981,23 @@
     <row r="135" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <f t="shared" si="5"/>
-        <v>2064600</v>
-      </c>
-      <c r="B135" s="8"/>
+        <v>2154600</v>
+      </c>
+      <c r="B135" s="8">
+        <v>90000</v>
+      </c>
       <c r="C135" s="8"/>
-      <c r="D135" s="1"/>
-      <c r="E135" s="1"/>
+      <c r="D135" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <f t="shared" si="5"/>
-        <v>2064600</v>
+        <v>2154600</v>
       </c>
       <c r="B136" s="8"/>
       <c r="C136" s="8"/>
@@ -2998,7 +3007,7 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>2064600</v>
+        <v>2154600</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -3008,7 +3017,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>2064600</v>
+        <v>2154600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -3019,7 +3028,7 @@
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>13965600</v>
+        <v>14055600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
@@ -3030,7 +3039,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>2064600</v>
+        <v>2154600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="183">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -562,6 +562,12 @@
   </si>
   <si>
     <t>1405/05/10</t>
+  </si>
+  <si>
+    <t>1405/05/17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پول </t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1093,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>2154600</v>
+        <v>2254600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2997,17 +3003,23 @@
     <row r="136" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <f t="shared" si="5"/>
-        <v>2154600</v>
-      </c>
-      <c r="B136" s="8"/>
+        <v>2254600</v>
+      </c>
+      <c r="B136" s="8">
+        <v>100000</v>
+      </c>
       <c r="C136" s="8"/>
-      <c r="D136" s="1"/>
-      <c r="E136" s="1"/>
+      <c r="D136" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>2154600</v>
+        <v>2254600</v>
       </c>
       <c r="B137" s="8"/>
       <c r="C137" s="8"/>
@@ -3017,7 +3029,7 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>2154600</v>
+        <v>2254600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -3028,7 +3040,7 @@
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>14055600</v>
+        <v>14155600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
@@ -3039,7 +3051,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>2154600</v>
+        <v>2254600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="184">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -568,6 +568,9 @@
   </si>
   <si>
     <t xml:space="preserve">پول </t>
+  </si>
+  <si>
+    <t>1405/05/18</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +1096,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>2254600</v>
+        <v>2514600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3019,17 +3022,23 @@
     <row r="137" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <f t="shared" si="5"/>
-        <v>2254600</v>
-      </c>
-      <c r="B137" s="8"/>
+        <v>2514600</v>
+      </c>
+      <c r="B137" s="8">
+        <v>260000</v>
+      </c>
       <c r="C137" s="8"/>
-      <c r="D137" s="1"/>
-      <c r="E137" s="1"/>
+      <c r="D137" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>2254600</v>
+        <v>2514600</v>
       </c>
       <c r="B138" s="8"/>
       <c r="C138" s="8"/>
@@ -3040,7 +3049,7 @@
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>14155600</v>
+        <v>14415600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
@@ -3051,7 +3060,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>2254600</v>
+        <v>2514600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="186">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -571,6 +571,12 @@
   </si>
   <si>
     <t>1405/05/18</t>
+  </si>
+  <si>
+    <t>1405/05/30</t>
+  </si>
+  <si>
+    <t>کیکدلستر سیگار نخی</t>
   </si>
 </sst>
 </file>
@@ -1096,7 +1102,7 @@
       </c>
       <c r="H2" s="9">
         <f>B141</f>
-        <v>2514600</v>
+        <v>2724600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3038,18 +3044,24 @@
     <row r="138" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <f t="shared" si="5"/>
-        <v>2514600</v>
-      </c>
-      <c r="B138" s="8"/>
+        <v>2724600</v>
+      </c>
+      <c r="B138" s="8">
+        <v>210000</v>
+      </c>
       <c r="C138" s="8"/>
-      <c r="D138" s="1"/>
-      <c r="E138" s="1"/>
+      <c r="D138" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="139" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="9"/>
       <c r="B139" s="9">
         <f>SUM(B119:B138)+B113</f>
-        <v>14415600</v>
+        <v>14625600</v>
       </c>
       <c r="C139" s="9">
         <f>SUM(C119:C138)+C113</f>
@@ -3060,7 +3072,7 @@
     <row r="141" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B141" s="10">
         <f>A138</f>
-        <v>2514600</v>
+        <v>2724600</v>
       </c>
       <c r="C141" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="188">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -577,6 +577,12 @@
   </si>
   <si>
     <t>کیکدلستر سیگار نخی</t>
+  </si>
+  <si>
+    <t>1405/06/05</t>
+  </si>
+  <si>
+    <t>بستنی لیموناد</t>
   </si>
 </sst>
 </file>
@@ -703,7 +709,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1064,7 +1091,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H153"/>
+  <dimension ref="A1:H266"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -1101,8 +1128,8 @@
         <v>7</v>
       </c>
       <c r="H2" s="9">
-        <f>B141</f>
-        <v>2724600</v>
+        <f>B167</f>
+        <v>2924600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2721,7 +2748,14 @@
         <v>57</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>17</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="118" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>4</v>
@@ -3087,23 +3121,386 @@
         <v>57</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>17</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D144" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A145" s="8">
+        <f xml:space="preserve"> B141+B145-C145</f>
+        <v>2924600</v>
+      </c>
+      <c r="B145" s="8">
+        <v>200000</v>
+      </c>
+      <c r="C145" s="8"/>
+      <c r="D145" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A146" s="8">
+        <f xml:space="preserve"> A145+B146-C146</f>
+        <v>2924600</v>
+      </c>
+      <c r="B146" s="8"/>
+      <c r="C146" s="8"/>
+      <c r="D146" s="1"/>
+      <c r="E146" s="1"/>
+    </row>
+    <row r="147" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A147" s="8">
+        <f t="shared" ref="A147:A164" si="6" xml:space="preserve"> A146+B147-C147</f>
+        <v>2924600</v>
+      </c>
+      <c r="B147" s="8"/>
+      <c r="C147" s="8"/>
+      <c r="D147" s="1"/>
+      <c r="E147" s="1"/>
+    </row>
+    <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A148" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B148" s="8"/>
+      <c r="C148" s="8"/>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
+    </row>
+    <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B149" s="8"/>
+      <c r="C149" s="8"/>
+      <c r="D149" s="1"/>
+      <c r="E149" s="1"/>
+    </row>
+    <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B150" s="8"/>
+      <c r="C150" s="8"/>
+      <c r="D150" s="1"/>
+      <c r="E150" s="1"/>
+    </row>
+    <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B151" s="8"/>
+      <c r="C151" s="8"/>
+      <c r="D151" s="1"/>
+      <c r="E151" s="1"/>
+    </row>
+    <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B152" s="8"/>
+      <c r="C152" s="8"/>
+      <c r="D152" s="1"/>
+      <c r="E152" s="1"/>
+    </row>
+    <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A153" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B153" s="8"/>
+      <c r="C153" s="8"/>
+      <c r="D153" s="1"/>
+      <c r="E153" s="1"/>
+    </row>
+    <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A154" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B154" s="8"/>
+      <c r="C154" s="8"/>
+      <c r="D154" s="1"/>
+      <c r="E154" s="1"/>
+    </row>
+    <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A155" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B155" s="8"/>
+      <c r="C155" s="8"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+    </row>
+    <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A156" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B156" s="8"/>
+      <c r="C156" s="8"/>
+      <c r="D156" s="1"/>
+      <c r="E156" s="1"/>
+    </row>
+    <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A157" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B157" s="8"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="1"/>
+      <c r="E157" s="1"/>
+    </row>
+    <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A158" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B158" s="8"/>
+      <c r="C158" s="8"/>
+      <c r="D158" s="1"/>
+      <c r="E158" s="1"/>
+    </row>
+    <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B159" s="8"/>
+      <c r="C159" s="8"/>
+      <c r="D159" s="1"/>
+      <c r="E159" s="1"/>
+    </row>
+    <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B160" s="8"/>
+      <c r="C160" s="8"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+    </row>
+    <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B161" s="8"/>
+      <c r="C161" s="8"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+    </row>
+    <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A162" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B162" s="8"/>
+      <c r="C162" s="8"/>
+      <c r="D162" s="1"/>
+      <c r="E162" s="1"/>
+    </row>
+    <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A163" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B163" s="8"/>
+      <c r="C163" s="8"/>
+      <c r="D163" s="1"/>
+      <c r="E163" s="1"/>
+    </row>
+    <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="8">
+        <f t="shared" si="6"/>
+        <v>2924600</v>
+      </c>
+      <c r="B164" s="8"/>
+      <c r="C164" s="8"/>
+      <c r="D164" s="1"/>
+      <c r="E164" s="1"/>
+    </row>
+    <row r="165" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="9"/>
+      <c r="B165" s="9">
+        <f>SUM(B145:B164)+B139</f>
+        <v>14825600</v>
+      </c>
+      <c r="C165" s="9">
+        <f>SUM(C145:C164)+C139</f>
+        <v>11901000</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B167" s="10">
+        <f>A164</f>
+        <v>2924600</v>
+      </c>
+      <c r="C167" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D167" s="15"/>
+    </row>
+    <row r="168" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B168" t="s">
+        <v>58</v>
+      </c>
+      <c r="D168" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="29.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="C63:D63"/>
     <mergeCell ref="C141:D141"/>
+    <mergeCell ref="C167:D167"/>
   </mergeCells>
   <conditionalFormatting sqref="B63">
+    <cfRule type="cellIs" dxfId="14" priority="17" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="19" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="20" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B89">
     <cfRule type="cellIs" dxfId="11" priority="13" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3117,7 +3514,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B89">
+  <conditionalFormatting sqref="B115">
     <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3131,7 +3528,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B115">
+  <conditionalFormatting sqref="B141">
     <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -3145,7 +3542,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B141">
+  <conditionalFormatting sqref="B167">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="190">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -583,6 +583,12 @@
   </si>
   <si>
     <t>بستنی لیموناد</t>
+  </si>
+  <si>
+    <t>1405/06/06</t>
+  </si>
+  <si>
+    <t>الباقی سیگار پفک</t>
   </si>
 </sst>
 </file>
@@ -1129,7 +1135,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3165,17 +3171,23 @@
     <row r="146" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
         <f xml:space="preserve"> A145+B146-C146</f>
-        <v>2924600</v>
-      </c>
-      <c r="B146" s="8"/>
+        <v>3074600</v>
+      </c>
+      <c r="B146" s="8">
+        <v>150000</v>
+      </c>
       <c r="C146" s="8"/>
-      <c r="D146" s="1"/>
-      <c r="E146" s="1"/>
+      <c r="D146" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="147" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <f t="shared" ref="A147:A164" si="6" xml:space="preserve"> A146+B147-C147</f>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B147" s="8"/>
       <c r="C147" s="8"/>
@@ -3185,7 +3197,7 @@
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
@@ -3195,7 +3207,7 @@
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
@@ -3205,7 +3217,7 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
@@ -3215,7 +3227,7 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -3225,7 +3237,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -3235,7 +3247,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -3245,7 +3257,7 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3255,7 +3267,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3265,7 +3277,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3275,7 +3287,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3285,7 +3297,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3295,7 +3307,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3305,7 +3317,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3315,7 +3327,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3325,7 +3337,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3335,7 +3347,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3345,7 +3357,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3356,7 +3368,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>14825600</v>
+        <v>14975600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3367,7 +3379,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>2924600</v>
+        <v>3074600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="192">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -589,6 +589,12 @@
   </si>
   <si>
     <t>الباقی سیگار پفک</t>
+  </si>
+  <si>
+    <t>1405/06/07</t>
+  </si>
+  <si>
+    <t>دنگ سوسیس خونه یاسین</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1141,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3187,17 +3193,23 @@
     <row r="147" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <f t="shared" ref="A147:A164" si="6" xml:space="preserve"> A146+B147-C147</f>
-        <v>3074600</v>
-      </c>
-      <c r="B147" s="8"/>
+        <v>3190600</v>
+      </c>
+      <c r="B147" s="8">
+        <v>116000</v>
+      </c>
       <c r="C147" s="8"/>
-      <c r="D147" s="1"/>
-      <c r="E147" s="1"/>
+      <c r="D147" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B148" s="8"/>
       <c r="C148" s="8"/>
@@ -3207,7 +3219,7 @@
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
@@ -3217,7 +3229,7 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
@@ -3227,7 +3239,7 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -3237,7 +3249,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -3247,7 +3259,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -3257,7 +3269,7 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3267,7 +3279,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3277,7 +3289,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3287,7 +3299,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3297,7 +3309,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3307,7 +3319,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3317,7 +3329,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3327,7 +3339,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3337,7 +3349,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3347,7 +3359,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3357,7 +3369,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3368,7 +3380,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>14975600</v>
+        <v>15091600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3379,7 +3391,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3074600</v>
+        <v>3190600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="193">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -595,6 +595,9 @@
   </si>
   <si>
     <t>دنگ سوسیس خونه یاسین</t>
+  </si>
+  <si>
+    <t>1405/06/18</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1144,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3209,17 +3212,23 @@
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
-      </c>
-      <c r="B148" s="8"/>
+        <v>3310600</v>
+      </c>
+      <c r="B148" s="8">
+        <v>120000</v>
+      </c>
       <c r="C148" s="8"/>
-      <c r="D148" s="1"/>
-      <c r="E148" s="1"/>
+      <c r="D148" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
@@ -3229,7 +3238,7 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
@@ -3239,7 +3248,7 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -3249,7 +3258,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -3259,7 +3268,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -3269,7 +3278,7 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3279,7 +3288,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3289,7 +3298,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3299,7 +3308,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3309,7 +3318,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3319,7 +3328,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3329,7 +3338,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3339,7 +3348,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3349,7 +3358,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3359,7 +3368,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3369,7 +3378,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3380,7 +3389,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15091600</v>
+        <v>15211600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3391,7 +3400,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3190600</v>
+        <v>3310600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>

--- a/customers/bofon.xlsx
+++ b/customers/bofon.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="192">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -595,9 +595,6 @@
   </si>
   <si>
     <t>دنگ سوسیس خونه یاسین</t>
-  </si>
-  <si>
-    <t>1405/06/18</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1141,7 @@
       </c>
       <c r="H2" s="9">
         <f>B167</f>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3212,23 +3209,17 @@
     <row r="148" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
-      </c>
-      <c r="B148" s="8">
-        <v>120000</v>
-      </c>
+        <v>3190600</v>
+      </c>
+      <c r="B148" s="8"/>
       <c r="C148" s="8"/>
-      <c r="D148" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="D148" s="1"/>
+      <c r="E148" s="1"/>
     </row>
     <row r="149" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B149" s="8"/>
       <c r="C149" s="8"/>
@@ -3238,7 +3229,7 @@
     <row r="150" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B150" s="8"/>
       <c r="C150" s="8"/>
@@ -3248,7 +3239,7 @@
     <row r="151" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B151" s="8"/>
       <c r="C151" s="8"/>
@@ -3258,7 +3249,7 @@
     <row r="152" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B152" s="8"/>
       <c r="C152" s="8"/>
@@ -3268,7 +3259,7 @@
     <row r="153" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B153" s="8"/>
       <c r="C153" s="8"/>
@@ -3278,7 +3269,7 @@
     <row r="154" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B154" s="8"/>
       <c r="C154" s="8"/>
@@ -3288,7 +3279,7 @@
     <row r="155" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B155" s="8"/>
       <c r="C155" s="8"/>
@@ -3298,7 +3289,7 @@
     <row r="156" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B156" s="8"/>
       <c r="C156" s="8"/>
@@ -3308,7 +3299,7 @@
     <row r="157" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B157" s="8"/>
       <c r="C157" s="8"/>
@@ -3318,7 +3309,7 @@
     <row r="158" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B158" s="8"/>
       <c r="C158" s="8"/>
@@ -3328,7 +3319,7 @@
     <row r="159" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B159" s="8"/>
       <c r="C159" s="8"/>
@@ -3338,7 +3329,7 @@
     <row r="160" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B160" s="8"/>
       <c r="C160" s="8"/>
@@ -3348,7 +3339,7 @@
     <row r="161" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B161" s="8"/>
       <c r="C161" s="8"/>
@@ -3358,7 +3349,7 @@
     <row r="162" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B162" s="8"/>
       <c r="C162" s="8"/>
@@ -3368,7 +3359,7 @@
     <row r="163" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B163" s="8"/>
       <c r="C163" s="8"/>
@@ -3378,7 +3369,7 @@
     <row r="164" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <f t="shared" si="6"/>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="B164" s="8"/>
       <c r="C164" s="8"/>
@@ -3389,7 +3380,7 @@
       <c r="A165" s="9"/>
       <c r="B165" s="9">
         <f>SUM(B145:B164)+B139</f>
-        <v>15211600</v>
+        <v>15091600</v>
       </c>
       <c r="C165" s="9">
         <f>SUM(C145:C164)+C139</f>
@@ -3400,7 +3391,7 @@
     <row r="167" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B167" s="10">
         <f>A164</f>
-        <v>3310600</v>
+        <v>3190600</v>
       </c>
       <c r="C167" s="15" t="s">
         <v>172</v>
